--- a/research/A股宏观面_指标可得性清单.xlsx
+++ b/research/A股宏观面_指标可得性清单.xlsx
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" style="11" min="1" max="1"/>
@@ -644,14 +644,14 @@
       <c r="C3" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>🔶 可近似</t>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>🟦 已爬取接入</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>对 A 股传导弱，框架自身权重低（0.7），以财新服务业 PMI 近似</t>
+          <t>财新服务业 PMI（macro_china_cx_services_pmi_yearly）代理</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>以 CPB 世界贸易量 + SOX + 铜油比等全球代理替代，不单独接 ISM</t>
+          <t>以 CPB 世界贸易量 + SOX + 铜油比等全球代理组合替代</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -854,14 +854,14 @@
       <c r="C9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>🔶 可近似</t>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>🟦 已爬取接入</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>近似：FRED DEXCHUS（在岸人民币汇率，日度）；东财 forex_hist_em('USDCNH') 可拿离岸但接口不稳</t>
+          <t>央行人民币中间价（currency_boc_safe，8000+ 行）代理；离岸 USDCNH 接口不稳未用</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -889,14 +889,14 @@
       <c r="C10" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>🔶 可近似</t>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>🟦 已爬取接入</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>近似：东财 futures_global_hist_em(品种代码)（代码表见 futures_global_spot_em，如 HG=铜、CL=原油）；或 FRED PCOPPUSDM（铜·月度）+ DCOILWTIC（WTI·日度）</t>
+          <t>FRED PCOPPUSDM（铜）÷ POILWTIUSDM（WTI 油），月度稳定序列</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2254,14 +2254,14 @@
       <c r="C49" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="D49" s="14" t="inlineStr">
-        <is>
-          <t>🔶 可近似</t>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>🟦 已爬取接入</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>信贷收支表已覆盖财政性存款；非银存款行名口径在不同表不一致，暂以财政性存款为主要流动性代理</t>
+          <t>央行信贷收支表「非存款类金融机构存款」余额</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>公开市场操作公告无结构化接口，以 DR007 变动近似（资金面页已有）</t>
+          <t>以 DR007 变动近似（资金面页已有 DR007/FDR007）</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>金融监管总局季度披露无稳定接口，权重低（0.7），暂以信贷收支负债端近似</t>
+          <t>以信贷收支负债端（非银存款+财政存款）近似，权重低(0.7)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>中债托管量接口不稳定，本期未做</t>
+          <t>以「社融政府债券存量同比 + 专项债发行额」联合代理准财政力度；单独接国开/进出口/农发债口径不稳且权重低(0.8)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -2604,14 +2604,14 @@
       <c r="C59" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>🔶 可近似</t>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>🟦 已爬取接入</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>近似：统计局 70 城房价（akshare macro_china_new_house_price 为新房口径；70 城上涨城市占比可算扩散度，需专门接入）</t>
+          <t>京沪二手住宅环比均值代理（akshare 仅含京沪，70 城扩散需逐城爬取未做）</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -2744,14 +2744,14 @@
       <c r="C63" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="D63" s="14" t="inlineStr">
-        <is>
-          <t>🔶 可近似</t>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>🟦 已爬取接入</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>依赖财政/信贷多源拼接，部分已由财政支出+信贷收支覆盖</t>
+          <t>财政支出+专项债发行+企事业中长期贷款三线合成执行确认分</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -3186,15 +3186,16 @@
       </c>
     </row>
     <row r="76"/>
-    <row r="78">
-      <c r="A78" s="16" t="inlineStr">
+    <row r="77"/>
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
         <is>
           <t>统计</t>
         </is>
       </c>
-      <c r="B78" s="16" t="inlineStr">
-        <is>
-          <t>共 74 项：⛔ 已剔除 2 项；✅ 可直接用 21 项；🔶 可近似 28 项；🟦 已爬取接入 23 项</t>
+      <c r="B79" s="16" t="inlineStr">
+        <is>
+          <t>共 74 项：⛔ 已剔除 2 项；✅ 可直接用 21 项；🔶 可近似 22 项；🟦 已爬取接入 29 项</t>
         </is>
       </c>
     </row>
